--- a/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,61; 86,15</t>
+          <t>68,87; 86,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,05; 88,93</t>
+          <t>79,75; 88,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,34; 86,94</t>
+          <t>76,59; 86,86</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,62; 82,4</t>
+          <t>68,22; 82,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,03; 84,84</t>
+          <t>73,75; 84,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,24; 81,44</t>
+          <t>72,54; 81,7</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69,42; 82,58</t>
+          <t>69,79; 82,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,1; 80,72</t>
+          <t>68,43; 80,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,44; 79,95</t>
+          <t>71,24; 80,29</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,65; 79,63</t>
+          <t>62,77; 80,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,42; 79,05</t>
+          <t>40,69; 79,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,66; 76,3</t>
+          <t>48,53; 76,57</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,15; 52,07</t>
+          <t>35,76; 51,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,64; 56,2</t>
+          <t>43,63; 55,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,86; 51,89</t>
+          <t>41,83; 51,49</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73,34; 85,9</t>
+          <t>72,82; 85,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75,56; 87,06</t>
+          <t>75,48; 87,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76,4; 85,16</t>
+          <t>76,56; 84,92</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,44; 81,18</t>
+          <t>71,16; 82,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,2; 94,78</t>
+          <t>73,09; 94,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,47; 91,46</t>
+          <t>74,38; 91,34</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,31; 85,26</t>
+          <t>77,39; 85,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,35; 91,79</t>
+          <t>86,24; 91,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82,6; 87,62</t>
+          <t>82,88; 87,65</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>73,01; 77,81</t>
+          <t>72,76; 78,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75,22; 85,5</t>
+          <t>75,24; 85,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75,22; 81,68</t>
+          <t>75,01; 81,51</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>107833; 135414</t>
+          <t>108248; 135463</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129095; 145234</t>
+          <t>130243; 144941</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>247859; 278644</t>
+          <t>245454; 278378</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>181424; 224405</t>
+          <t>185778; 224499</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173224; 198516</t>
+          <t>172575; 197643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>365751; 412377</t>
+          <t>367312; 413662</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>129679; 154255</t>
+          <t>130361; 154985</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>125353; 146440</t>
+          <t>124145; 145822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263040; 294377</t>
+          <t>262306; 295630</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105535; 136306</t>
+          <t>107446; 137693</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83452; 181145</t>
+          <t>93234; 182322</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>198793; 305468</t>
+          <t>194276; 306535</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36127; 53512</t>
+          <t>36752; 52896</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56134; 72287</t>
+          <t>56124; 71279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96871; 120074</t>
+          <t>96785; 119147</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>103560; 121298</t>
+          <t>102833; 120667</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>106068; 122215</t>
+          <t>105954; 122402</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>215141; 239809</t>
+          <t>215576; 239129</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>197826; 227987</t>
+          <t>199829; 230995</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>363863; 471104</t>
+          <t>363323; 470675</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>579283; 711442</t>
+          <t>578595; 710540</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>264953; 292194</t>
+          <t>265227; 293255</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>288288; 306447</t>
+          <t>287917; 306444</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>558876; 592813</t>
+          <t>560770; 593031</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1208325; 1287758</t>
+          <t>1204150; 1291266</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1434953; 1631081</t>
+          <t>1435429; 1623612</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2679933; 2910240</t>
+          <t>2672528; 2904034</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,87; 86,19</t>
+          <t>75,79; 87,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,75; 88,75</t>
+          <t>80,68; 88,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,59; 86,86</t>
+          <t>80,18; 87,63</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,22; 82,43</t>
+          <t>67,48; 82,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,75; 84,46</t>
+          <t>74,98; 84,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,54; 81,7</t>
+          <t>73,51; 81,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69,79; 82,97</t>
+          <t>70,6; 83,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,43; 80,38</t>
+          <t>69,71; 81,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,24; 80,29</t>
+          <t>72,02; 81,09</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,77; 80,44</t>
+          <t>62,5; 79,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,69; 79,56</t>
+          <t>72,15; 82,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,53; 76,57</t>
+          <t>69,81; 79,95</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,76; 51,47</t>
+          <t>35,72; 51,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,63; 55,42</t>
+          <t>43,6; 55,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,83; 51,49</t>
+          <t>42,13; 51,52</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72,82; 85,45</t>
+          <t>73,79; 85,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75,48; 87,19</t>
+          <t>76,6; 88,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76,56; 84,92</t>
+          <t>77,26; 85,19</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,16; 82,25</t>
+          <t>68,63; 79,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,09; 94,69</t>
+          <t>68,45; 77,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,38; 91,34</t>
+          <t>69,81; 77,1</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,39; 85,57</t>
+          <t>78,5; 86,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,24; 91,79</t>
+          <t>86,51; 91,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82,88; 87,65</t>
+          <t>83,42; 88,16</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>72,76; 78,02</t>
+          <t>73,32; 78,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75,24; 85,1</t>
+          <t>76,73; 80,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75,01; 81,51</t>
+          <t>75,81; 78,55</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>125527</t>
+          <t>135857</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264063</t>
+          <t>287037</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108248; 135463</t>
+          <t>124716; 143782</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>130243; 144941</t>
+          <t>143093; 157559</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>245454; 278378</t>
+          <t>274136; 299626</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>205530</t>
+          <t>206721</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>187220</t>
+          <t>198117</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392750</t>
+          <t>404838</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>185778; 224499</t>
+          <t>184173; 224542</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>172575; 197643</t>
+          <t>185095; 208766</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>367312; 413662</t>
+          <t>382104; 425856</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>143161</t>
+          <t>146913</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>142257</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279754</t>
+          <t>289170</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>130361; 154985</t>
+          <t>134095; 158512</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>124145; 145822</t>
+          <t>130433; 152075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>262306; 295630</t>
+          <t>271558; 305756</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>123232</t>
+          <t>143871</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>151967</t>
+          <t>172251</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275199</t>
+          <t>316122</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>107446; 137693</t>
+          <t>124169; 158284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93234; 182322</t>
+          <t>159066; 182871</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194276; 306535</t>
+          <t>292611; 335084</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>49413</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63659</t>
+          <t>68324</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107804</t>
+          <t>117738</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36752; 52896</t>
+          <t>40452; 58207</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56124; 71279</t>
+          <t>60420; 76879</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96785; 119147</t>
+          <t>106099; 129739</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>112848</t>
+          <t>112693</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>115671</t>
+          <t>118672</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228519</t>
+          <t>231365</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>102833; 120667</t>
+          <t>103286; 119890</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>105954; 122402</t>
+          <t>109747; 126081</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>215576; 239129</t>
+          <t>218838; 241291</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>215544</t>
+          <t>238917</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>423244</t>
+          <t>262104</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>638788</t>
+          <t>501022</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>199829; 230995</t>
+          <t>220664; 256412</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>363323; 470675</t>
+          <t>244393; 275557</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>578595; 710540</t>
+          <t>473737; 523159</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>280082</t>
+          <t>330985</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>297689</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>577772</t>
+          <t>675342</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>265227; 293255</t>
+          <t>314153; 344822</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>287917; 306444</t>
+          <t>333779; 354810</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>560770; 593031</t>
+          <t>655698; 692937</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1250069</t>
+          <t>1365372</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1514580</t>
+          <t>1457263</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2764650</t>
+          <t>2822634</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1204150; 1291266</t>
+          <t>1320587; 1407764</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1435429; 1623612</t>
+          <t>1424488; 1486307</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2672528; 2904034</t>
+          <t>2772875; 2873058</t>
         </is>
       </c>
     </row>
